--- a/students.xlsx
+++ b/students.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Distinction</t>
+          <t>distinction</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,50 @@
           <t>072343456</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>25040308</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>KAREN</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mechatronics</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>071234567</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>25040308</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WENDY </t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pharmacy</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0787654322</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
